--- a/dcf/SNPS.xlsx
+++ b/dcf/SNPS.xlsx
@@ -452,7 +452,7 @@
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
       <text>
-        <t>Opus: 18.0x</t>
+        <t>User-edited — overridden from Opus 18.0x</t>
       </text>
     </comment>
     <comment ref="B46" authorId="0" shapeId="0">
@@ -1148,184 +1148,184 @@
     </row>
     <row r="5">
       <c r="A5" s="53" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>303.5773037068296</v>
+        <v>313.4331536647263</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>289.7451123870322</v>
+        <v>299.1553001230366</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>276.5614052968871</v>
+        <v>285.5479978609789</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>263.9923088898958</v>
+        <v>272.5761867050689</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>252.0058791626288</v>
+        <v>260.2068048422501</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>240.5719831305423</v>
+        <v>248.4086660168619</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>229.6621880960735</v>
+        <v>237.1523448036706</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="53" t="n">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>320.0037203033241</v>
+        <v>329.8595702612208</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>305.4287586137061</v>
+        <v>314.8389463497105</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>291.5390595703735</v>
+        <v>300.5256521344653</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>278.2987719151843</v>
+        <v>286.8826497303575</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>265.6740886286643</v>
+        <v>273.8750143082855</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>253.6331212744081</v>
+        <v>261.4698041607276</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>242.1457826087353</v>
+        <v>249.6359393163324</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="53" t="n">
-        <v>17</v>
+        <v>17.6</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>336.4301368998186</v>
+        <v>346.2859868577153</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>321.11240484038</v>
+        <v>330.5225925763844</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>306.5167138438599</v>
+        <v>315.5033064079518</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>292.6052349404729</v>
+        <v>301.189112755646</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>279.3422980946996</v>
+        <v>287.5432237743209</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>266.6942594182739</v>
+        <v>274.5309423045934</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>254.6293771213971</v>
+        <v>262.1195338289942</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="53" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>352.856553496313</v>
+        <v>362.7124034542097</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>336.7960510670539</v>
+        <v>346.2062388030583</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>321.4943681173463</v>
+        <v>330.4809606814382</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>306.9116979657614</v>
+        <v>315.4955757809345</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>293.010507560735</v>
+        <v>301.2114332403563</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>279.7553975621398</v>
+        <v>287.5920804484593</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>267.1129716340589</v>
+        <v>274.603128341656</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="53" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>369.2829700928075</v>
+        <v>379.1388200507042</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>352.4796972937278</v>
+        <v>361.8898850297322</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>336.4720223908327</v>
+        <v>345.4586149549246</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>321.21816099105</v>
+        <v>329.8020388062232</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>306.6787170267705</v>
+        <v>314.8796427063917</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>292.8165357060055</v>
+        <v>300.6532185923251</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>279.5965661467207</v>
+        <v>287.0867228543178</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="53" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>385.7093866893021</v>
+        <v>395.5652366471987</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>368.1633435204017</v>
+        <v>377.5735312564061</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>351.4496766643191</v>
+        <v>360.436269228411</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>335.5246240163385</v>
+        <v>344.1085018315117</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>320.3469264928058</v>
+        <v>328.5478521724271</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>305.8776738498713</v>
+        <v>313.7143567361908</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>292.0801606593824</v>
+        <v>299.5703173669795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="53" t="n">
-        <v>21</v>
+        <v>21.6</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>402.1358032857965</v>
+        <v>411.9916532436932</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>383.8469897470757</v>
+        <v>393.2571774830799</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>366.4273309378056</v>
+        <v>375.4139235018975</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>349.8310870416271</v>
+        <v>358.4149648568003</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>334.0151359588412</v>
+        <v>342.2160616384625</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>318.9388119937372</v>
+        <v>326.7754948800567</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>304.5637551720442</v>
+        <v>312.0539118796414</v>
       </c>
     </row>
     <row r="13">
@@ -1348,7 +1348,7 @@
         <v>0.09306249061386392</v>
       </c>
       <c r="C14" s="57" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
     </row>
   </sheetData>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.8530692324504309</v>
+        <v>0.8522768025618864</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24427,7 +24427,7 @@
         </is>
       </c>
       <c r="B45" s="19" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="46">
@@ -24624,13 +24624,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>306.9116979657614</v>
+        <v>315.4955757809345</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>431.4616119585659</v>
+        <v>442.3273295787582</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>212.1188149406431</v>
+        <v>218.8542297074232</v>
       </c>
     </row>
     <row r="59">
@@ -25338,9 +25338,9 @@
         <f>Dashboard!B45</f>
         <v/>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Opus</t>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>user-edited</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -25348,7 +25348,11 @@
           <t>18.0x</t>
         </is>
       </c>
-      <c r="F36" s="31" t="inlineStr"/>
+      <c r="F36" s="31" t="inlineStr">
+        <is>
+          <t>overridden from Opus 18.0x</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">

--- a/dcf/SNPS.xlsx
+++ b/dcf/SNPS.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1151,25 +1151,25 @@
         <v>15.6</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>313.4331536647263</v>
+        <v>278.1953449289466</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>299.1553001230366</v>
+        <v>265.4312927129754</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>285.5479978609789</v>
+        <v>253.2649110612121</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>272.5761867050689</v>
+        <v>241.6649904680427</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>260.2068048422501</v>
+        <v>230.6020991396061</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>248.4086660168619</v>
+        <v>220.0484737912119</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>237.1523448036706</v>
+        <v>209.9779176247106</v>
       </c>
     </row>
     <row r="6">
@@ -1177,25 +1177,25 @@
         <v>16.6</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>329.8595702612208</v>
+        <v>292.7893380797697</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>314.8389463497105</v>
+        <v>279.3653740914337</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>300.5256521344653</v>
+        <v>266.5717563246707</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>286.8826497303575</v>
+        <v>254.3755181827801</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>273.8750143082855</v>
+        <v>242.7455726817239</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>261.4698041607276</v>
+        <v>231.6525969116624</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>249.6359393163324</v>
+        <v>221.0689240986558</v>
       </c>
     </row>
     <row r="7">
@@ -1203,25 +1203,25 @@
         <v>17.6</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>346.2859868577153</v>
+        <v>307.3833312305928</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>330.5225925763844</v>
+        <v>293.299455469892</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>315.5033064079518</v>
+        <v>279.8786015881291</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>301.189112755646</v>
+        <v>267.0860458975175</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>287.5432237743209</v>
+        <v>254.8890462238419</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>274.5309423045934</v>
+        <v>243.2567200321128</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>262.1195338289942</v>
+        <v>232.1599305726008</v>
       </c>
     </row>
     <row r="8">
@@ -1229,25 +1229,25 @@
         <v>18.6</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>362.7124034542097</v>
+        <v>321.9773243814159</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>346.2062388030583</v>
+        <v>307.2335368483502</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>330.4809606814382</v>
+        <v>293.1854468515875</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>315.4955757809345</v>
+        <v>279.7965736122549</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>301.2114332403563</v>
+        <v>267.0325197659598</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>287.5920804484593</v>
+        <v>254.8608431525632</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>274.603128341656</v>
+        <v>243.2509370465459</v>
       </c>
     </row>
     <row r="9">
@@ -1255,25 +1255,25 @@
         <v>19.6</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>379.1388200507042</v>
+        <v>336.571317532239</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>361.8898850297322</v>
+        <v>321.1676182268085</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>345.4586149549246</v>
+        <v>306.4922921150459</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>329.8020388062232</v>
+        <v>292.5071013269923</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>314.8796427063917</v>
+        <v>279.1759933080776</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>300.6532185923251</v>
+        <v>266.4649662730137</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>287.0867228543178</v>
+        <v>254.341943520491</v>
       </c>
     </row>
     <row r="10">
@@ -1281,25 +1281,25 @@
         <v>20.6</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>395.5652366471987</v>
+        <v>351.1653106830622</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>377.5735312564061</v>
+        <v>335.1016996052669</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>360.436269228411</v>
+        <v>319.7991373785044</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>344.1085018315117</v>
+        <v>305.2176290417297</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>328.5478521724271</v>
+        <v>291.3194668501955</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>313.7143567361908</v>
+        <v>278.0690893934641</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>299.5703173669795</v>
+        <v>265.4329499944361</v>
       </c>
     </row>
     <row r="11">
@@ -1307,25 +1307,25 @@
         <v>21.6</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>411.9916532436932</v>
+        <v>365.7593038338854</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>393.2571774830799</v>
+        <v>349.0357809837251</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>375.4139235018975</v>
+        <v>333.1059826419628</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>358.4149648568003</v>
+        <v>317.9281567564671</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>342.2160616384625</v>
+        <v>303.4629403923133</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>326.7754948800567</v>
+        <v>289.6732125139146</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>312.0539118796414</v>
+        <v>276.5239564683812</v>
       </c>
     </row>
     <row r="13">
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.8522768025618864</v>
+        <v>0.8533641230921515</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24472,7 +24472,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24624,13 +24624,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>315.4955757809345</v>
+        <v>279.7965736122549</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>442.3273295787582</v>
+        <v>383.4844504939443</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>218.8542297074232</v>
+        <v>198.6517847960126</v>
       </c>
     </row>
     <row r="59">
